--- a/Examples/HybridPowerSystem/Hybrid_4Bus/Transfverter_4Bus.xlsx
+++ b/Examples/HybridPowerSystem/Hybrid_4Bus/Transfverter_4Bus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gzhan\Documents\Imperial College London\PhD Year 1\Hybrid ACDC\Simplus-Grid-Tool-2025May_HybridACDC\Simplus-Grid-Tool\Examples\HybridPowerSystem\Hybrid_4Bus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80F3F1C-6B0F-4CC1-8FC1-75F201AF8CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D00E78-82CD-409B-9DC3-F4E9C7E91838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-120" windowWidth="24220" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4800" yWindow="1600" windowWidth="19200" windowHeight="10100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -664,14 +664,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="10.6328125" customWidth="1"/>
+    <col min="10" max="10" width="11.08984375" customWidth="1"/>
+    <col min="11" max="11" width="10.08984375" customWidth="1"/>
+    <col min="12" max="12" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -771,13 +771,13 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -809,13 +809,13 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -847,13 +847,13 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -918,36 +918,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34645F5B-1D7A-4323-9AD6-5FF81941CA24}">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9.90625" customWidth="1"/>
+    <col min="2" max="2" width="39.54296875" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" customWidth="1"/>
-    <col min="11" max="11" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" customWidth="1"/>
+    <col min="7" max="7" width="13.90625" customWidth="1"/>
+    <col min="8" max="8" width="15.08984375" customWidth="1"/>
+    <col min="9" max="9" width="18.6328125" customWidth="1"/>
+    <col min="10" max="10" width="18.54296875" customWidth="1"/>
+    <col min="11" max="11" width="17.08984375" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" customWidth="1"/>
+    <col min="14" max="14" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:17">
       <c r="A1" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:17">
       <c r="A2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:17">
       <c r="A3" s="3" t="s">
         <v>54</v>
       </c>
@@ -958,12 +958,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2"/>
       <c r="F4" s="2"/>
@@ -972,26 +972,33 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
         <v>60</v>
       </c>
       <c r="B5">
         <v>2010</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="1"/>
+      <c r="E5" s="1"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
   </sheetData>
@@ -1004,9 +1011,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D00B5E-E2E7-41B8-8388-8931D474EA96}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1092,10 +1099,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0C2B6E-74BD-40FA-8EB6-D64D8C21837A}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1309,12 +1316,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB93A31-1E5A-4104-8C10-8E6599437516}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1332,8 +1339,8 @@
         <v>9</v>
       </c>
       <c r="B3" s="1">
-        <f>B4*1000/2*5</f>
-        <v>125000</v>
+        <f>B4*1000*4</f>
+        <v>200000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1370,9 +1377,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EFCB373-2341-40B6-A375-7BA50357479A}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="1" max="1" width="30.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
